--- a/01-delivered-case-studies/komfort-place-signature-digital-growth/Excel/Project_Workbook.xlsx
+++ b/01-delivered-case-studies/komfort-place-signature-digital-growth/Excel/Project_Workbook.xlsx
@@ -459,6 +459,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="10">
       <c r="A3" s="12" t="inlineStr">
         <is>
@@ -491,7 +492,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Digital Product Lead and Business Analyst</t>
+          <t>Business Analyst (Contract)</t>
         </is>
       </c>
     </row>
@@ -507,6 +508,8 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="10">
       <c r="A9" s="14" t="inlineStr">
         <is>
@@ -652,6 +655,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="10">
       <c r="A19" s="16" t="inlineStr">
         <is>
@@ -2011,7 +2015,7 @@
       </c>
       <c r="E2" s="18" t="inlineStr">
         <is>
-          <t>Digital product lead</t>
+          <t>Business analyst</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2042,7 @@
       </c>
       <c r="E3" s="18" t="inlineStr">
         <is>
-          <t>Digital product lead</t>
+          <t>Business analyst</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2096,7 @@
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>Digital product lead</t>
+          <t>Business analyst</t>
         </is>
       </c>
     </row>
